--- a/Shared/XLS/Gacha.xlsx
+++ b/Shared/XLS/Gacha.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="18" r:id="rId1"/>
@@ -41,7 +41,7 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -58,7 +58,7 @@
       </rPr>
       <t>rade</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -75,7 +75,7 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -92,7 +92,7 @@
       </rPr>
       <t>achaID</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -109,55 +109,51 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>GachaTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>GachaInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!GachaTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>GachaType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CurrencyInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -174,71 +170,71 @@
       </rPr>
       <t>urrencyCost</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>일반장비 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>고급 장비 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>일반 스킬 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>고급 스킬 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>일반~에픽 장비 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>매직~레전드 장비 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>2~5성 스킬 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>1~4성 스킬 뽑기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -255,31 +251,43 @@
       </rPr>
       <t>eight</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ItemGradeTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Gacha_Equipment</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Currency</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ItemGradeType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -437,15 +445,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -453,24 +461,33 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -479,16 +496,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -868,7 +879,7 @@
       <c r="B23" s="13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -929,10 +940,10 @@
         <v>16</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -949,16 +960,16 @@
         <v>12</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>4</v>
@@ -978,13 +989,13 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1">
         <v>2000</v>
@@ -1003,13 +1014,13 @@
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1">
         <v>200</v>
@@ -1028,13 +1039,13 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1">
         <v>2000</v>
@@ -1053,13 +1064,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="1">
         <v>200</v>
@@ -1104,7 +1115,7 @@
       <c r="N18" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1138,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F1" s="11"/>
     </row>
@@ -1154,7 +1165,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2"/>
       <c r="G2" s="12"/>
@@ -1170,11 +1181,11 @@
       <c r="C3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>37</v>
+      <c r="D3" s="17" t="s">
+        <v>39</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F3"/>
       <c r="G3" s="12"/>
@@ -1191,7 +1202,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1">
         <v>660000</v>
@@ -1216,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1">
         <v>280000</v>
@@ -1234,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1">
         <v>59000</v>
@@ -1252,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1">
         <v>1000</v>
@@ -1268,7 +1279,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>648900</v>
@@ -1284,7 +1295,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
         <v>350000</v>
@@ -1300,7 +1311,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1">
         <v>1000</v>
@@ -1316,7 +1327,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>
@@ -1339,7 +1350,7 @@
       <c r="C20" s="13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
